--- a/МО 19.10.2026/Учет медосмотров (ред. 19.10.2026).xlsx
+++ b/МО 19.10.2026/Учет медосмотров (ред. 19.10.2026).xlsx
@@ -299,7 +299,7 @@
     <t xml:space="preserve">Пункты Приказа №29н: оператору склада (п.16) установлены п.4.4, п.5.1, п.6.2 (ранее п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.6.2, п.18.1); кладовщик-комплектовщик выделен из п.14 в отдельную позицию п.46 с пунктами п.4.3.1, п.4.3.2, п.4.4, п.5.1, п.6.2, п.18.1 (ранее п.4.4, п.5.1, п.6.2) и отнесён к подлежащим психиатрическому освидетельствованию (п.1 Прил.№2 к Приказу №342н).</t>
   </si>
   <si>
-    <t xml:space="preserve">Сверка со штатным расписанием на 19.10.2026: добавлено 6 работников (Архипенко О.Д., Вавилин А.А., Котов К.О., Грачев А.Н., Решилова Ю.Е., Зайцев А.В.), исключено 2 (уволены: Трофимов В.Д., Первоченков В.В.); у 96 работников должность и (или) подразделение приведены к штатному расписанию.</t>
+    <t xml:space="preserve">Сверка со штатным расписанием на 19.10.2026: добавлено 6 работников (Архипенко О.Д., Вавилин А.А., Котов К.О., Грачев А.Н., Решилова Ю.Е., Зайцев А.В.; дата предварительного осмотра 01.10.2026), исключено 2 (уволены: Трофимов В.Д., Первоченков В.В.); у 96 работников должность и (или) подразделение приведены к штатному расписанию.</t>
   </si>
   <si>
     <t xml:space="preserve">Не включены в учёт: Гапеенко Э.В. (специалист, Москва) — по решению от 15.10.2026 для специалистов Москвы.</t>
@@ -3915,11 +3915,11 @@
       </c>
       <c r="B8" s="15" t="n">
         <f aca="false">COUNTIF('Учёт медосмотров'!$K$6:$K$405,"&lt;&gt;")</f>
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C8" s="16" t="n">
         <f aca="false">IF($B$7=0,"",B8/$B$7)</f>
-        <v>0.208672086720867</v>
+        <v>0.224932249322493</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3928,11 +3928,11 @@
       </c>
       <c r="B9" s="17" t="n">
         <f aca="false">COUNTIFS('Учёт медосмотров'!$C$6:$C$405,"&lt;&gt;",'Учёт медосмотров'!$K$6:$K$405,"")</f>
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="C9" s="16" t="n">
         <f aca="false">IF($B$7=0,"",B9/$B$7)</f>
-        <v>0.791327913279133</v>
+        <v>0.775067750677507</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3967,11 +3967,11 @@
       </c>
       <c r="B12" s="18" t="n">
         <f aca="false">COUNTIF('Учёт медосмотров'!$R$6:$R$405,"В срок")</f>
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C12" s="16" t="n">
         <f aca="false">IF($B$7=0,"",B12/$B$7)</f>
-        <v>0.100271002710027</v>
+        <v>0.116531165311653</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4006,11 +4006,11 @@
       </c>
       <c r="B15" s="19" t="n">
         <f aca="false">COUNTIF('Учёт медосмотров'!$R$6:$R$405,"Нет сведений")</f>
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="C15" s="16" t="n">
         <f aca="false">IF($B$7=0,"",B15/$B$7)</f>
-        <v>0.791327913279133</v>
+        <v>0.775067750677507</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4177,7 +4177,7 @@
       </c>
       <c r="C28" s="21" t="n">
         <f aca="false">COUNTIFS('Учёт медосмотров'!$B$6:$B$405,$A28,'Учёт медосмотров'!$R$6:$R$405,"В срок")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D28" s="21" t="n">
         <f aca="false">COUNTIFS('Учёт медосмотров'!$B$6:$B$405,$A28,'Учёт медосмотров'!$R$6:$R$405,"Истекает")</f>
@@ -4189,7 +4189,7 @@
       </c>
       <c r="F28" s="21" t="n">
         <f aca="false">COUNTIFS('Учёт медосмотров'!$B$6:$B$405,$A28,'Учёт медосмотров'!$R$6:$R$405,"Нет сведений")</f>
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G28" s="21" t="n">
         <f aca="false">COUNTIFS('Учёт медосмотров'!$B$6:$B$405,$A28,'Учёт медосмотров'!$N$6:$N$405,"Да")</f>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="C31" s="21" t="n">
         <f aca="false">COUNTIFS('Учёт медосмотров'!$B$6:$B$405,$A31,'Учёт медосмотров'!$R$6:$R$405,"В срок")</f>
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D31" s="21" t="n">
         <f aca="false">COUNTIFS('Учёт медосмотров'!$B$6:$B$405,$A31,'Учёт медосмотров'!$R$6:$R$405,"Истекает")</f>
@@ -4288,7 +4288,7 @@
       </c>
       <c r="F31" s="21" t="n">
         <f aca="false">COUNTIFS('Учёт медосмотров'!$B$6:$B$405,$A31,'Учёт медосмотров'!$R$6:$R$405,"Нет сведений")</f>
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="G31" s="21" t="n">
         <f aca="false">COUNTIFS('Учёт медосмотров'!$B$6:$B$405,$A31,'Учёт медосмотров'!$N$6:$N$405,"Да")</f>
@@ -4342,7 +4342,7 @@
       </c>
       <c r="C33" s="21" t="n">
         <f aca="false">COUNTIFS('Учёт медосмотров'!$B$6:$B$405,$A33,'Учёт медосмотров'!$R$6:$R$405,"В срок")</f>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D33" s="21" t="n">
         <f aca="false">COUNTIFS('Учёт медосмотров'!$B$6:$B$405,$A33,'Учёт медосмотров'!$R$6:$R$405,"Истекает")</f>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="F33" s="21" t="n">
         <f aca="false">COUNTIFS('Учёт медосмотров'!$B$6:$B$405,$A33,'Учёт медосмотров'!$R$6:$R$405,"Нет сведений")</f>
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G33" s="21" t="n">
         <f aca="false">COUNTIFS('Учёт медосмотров'!$B$6:$B$405,$A33,'Учёт медосмотров'!$N$6:$N$405,"Да")</f>
@@ -4408,7 +4408,7 @@
       </c>
       <c r="C35" s="23" t="n">
         <f aca="false">SUM(C27:C34)</f>
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D35" s="23" t="n">
         <f aca="false">SUM(D27:D34)</f>
@@ -4420,7 +4420,7 @@
       </c>
       <c r="F35" s="23" t="n">
         <f aca="false">SUM(F27:F34)</f>
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="G35" s="23" t="n">
         <f aca="false">SUM(G27:G34)</f>
@@ -17825,11 +17825,13 @@
         <f aca="false">IF(C211="","",IFERROR(INDEX(Перечень!$D$6:$D$51,MATCH(H211,Перечень!$A$6:$A$51,0)),12))</f>
         <v>12</v>
       </c>
-      <c r="K211" s="40"/>
+      <c r="K211" s="40" t="n">
+        <v>46296</v>
+      </c>
       <c r="L211" s="40"/>
-      <c r="M211" s="37" t="str">
+      <c r="M211" s="37" t="n">
         <f aca="false">IF(AND(K211="",L211=""),"",EDATE(MAX(K211,L211),J211))</f>
-        <v/>
+        <v>46661</v>
       </c>
       <c r="N211" s="41" t="str">
         <f aca="false">IF(C211="","",IFERROR(INDEX(Перечень!$F$6:$F$51,MATCH(H211,Перечень!$A$6:$A$51,0)),""))</f>
@@ -17846,7 +17848,7 @@
       </c>
       <c r="R211" s="41" t="str">
         <f aca="true">IF(C211="","",IF(M211="","Нет сведений",IF(M211&lt;TODAY(),"Просрочен",IF(M211-TODAY()&lt;=30,"Истекает","В срок"))))</f>
-        <v>Нет сведений</v>
+        <v>В срок</v>
       </c>
       <c r="S211" s="41" t="str">
         <f aca="false">IF(AND(N211="Да",O211=""),"Не пройдено","")</f>
@@ -26211,11 +26213,13 @@
         <f aca="false">IF(C341="","",IFERROR(INDEX(Перечень!$D$6:$D$51,MATCH(H341,Перечень!$A$6:$A$51,0)),12))</f>
         <v>12</v>
       </c>
-      <c r="K341" s="40"/>
+      <c r="K341" s="40" t="n">
+        <v>46296</v>
+      </c>
       <c r="L341" s="40"/>
-      <c r="M341" s="37" t="str">
+      <c r="M341" s="37" t="n">
         <f aca="false">IF(AND(K341="",L341=""),"",EDATE(MAX(K341,L341),J341))</f>
-        <v/>
+        <v>46661</v>
       </c>
       <c r="N341" s="41" t="str">
         <f aca="false">IF(C341="","",IFERROR(INDEX(Перечень!$F$6:$F$51,MATCH(H341,Перечень!$A$6:$A$51,0)),""))</f>
@@ -26232,7 +26236,7 @@
       </c>
       <c r="R341" s="41" t="str">
         <f aca="true">IF(C341="","",IF(M341="","Нет сведений",IF(M341&lt;TODAY(),"Просрочен",IF(M341-TODAY()&lt;=30,"Истекает","В срок"))))</f>
-        <v>Нет сведений</v>
+        <v>В срок</v>
       </c>
       <c r="S341" s="41" t="str">
         <f aca="false">IF(AND(N341="Да",O341=""),"Не пройдено","")</f>
@@ -26533,11 +26537,13 @@
         <f aca="false">IF(C346="","",IFERROR(INDEX(Перечень!$D$6:$D$51,MATCH(H346,Перечень!$A$6:$A$51,0)),12))</f>
         <v>12</v>
       </c>
-      <c r="K346" s="40"/>
+      <c r="K346" s="40" t="n">
+        <v>46296</v>
+      </c>
       <c r="L346" s="40"/>
-      <c r="M346" s="37" t="str">
+      <c r="M346" s="37" t="n">
         <f aca="false">IF(AND(K346="",L346=""),"",EDATE(MAX(K346,L346),J346))</f>
-        <v/>
+        <v>46661</v>
       </c>
       <c r="N346" s="41" t="str">
         <f aca="false">IF(C346="","",IFERROR(INDEX(Перечень!$F$6:$F$51,MATCH(H346,Перечень!$A$6:$A$51,0)),""))</f>
@@ -26554,7 +26560,7 @@
       </c>
       <c r="R346" s="41" t="str">
         <f aca="true">IF(C346="","",IF(M346="","Нет сведений",IF(M346&lt;TODAY(),"Просрочен",IF(M346-TODAY()&lt;=30,"Истекает","В срок"))))</f>
-        <v>Нет сведений</v>
+        <v>В срок</v>
       </c>
       <c r="S346" s="41" t="str">
         <f aca="false">IF(AND(N346="Да",O346=""),"Не пройдено","")</f>
@@ -27249,11 +27255,13 @@
         <f aca="false">IF(C357="","",IFERROR(INDEX(Перечень!$D$6:$D$51,MATCH(H357,Перечень!$A$6:$A$51,0)),12))</f>
         <v>12</v>
       </c>
-      <c r="K357" s="40"/>
+      <c r="K357" s="40" t="n">
+        <v>46296</v>
+      </c>
       <c r="L357" s="40"/>
-      <c r="M357" s="37" t="str">
+      <c r="M357" s="37" t="n">
         <f aca="false">IF(AND(K357="",L357=""),"",EDATE(MAX(K357,L357),J357))</f>
-        <v/>
+        <v>46661</v>
       </c>
       <c r="N357" s="41" t="str">
         <f aca="false">IF(C357="","",IFERROR(INDEX(Перечень!$F$6:$F$51,MATCH(H357,Перечень!$A$6:$A$51,0)),""))</f>
@@ -27270,7 +27278,7 @@
       </c>
       <c r="R357" s="41" t="str">
         <f aca="true">IF(C357="","",IF(M357="","Нет сведений",IF(M357&lt;TODAY(),"Просрочен",IF(M357-TODAY()&lt;=30,"Истекает","В срок"))))</f>
-        <v>Нет сведений</v>
+        <v>В срок</v>
       </c>
       <c r="S357" s="41" t="str">
         <f aca="false">IF(AND(N357="Да",O357=""),"Не пройдено","")</f>
@@ -27637,11 +27645,13 @@
         <f aca="false">IF(C363="","",IFERROR(INDEX(Перечень!$D$6:$D$51,MATCH(H363,Перечень!$A$6:$A$51,0)),12))</f>
         <v>12</v>
       </c>
-      <c r="K363" s="40"/>
+      <c r="K363" s="40" t="n">
+        <v>46296</v>
+      </c>
       <c r="L363" s="40"/>
-      <c r="M363" s="37" t="str">
+      <c r="M363" s="37" t="n">
         <f aca="false">IF(AND(K363="",L363=""),"",EDATE(MAX(K363,L363),J363))</f>
-        <v/>
+        <v>46661</v>
       </c>
       <c r="N363" s="41" t="str">
         <f aca="false">IF(C363="","",IFERROR(INDEX(Перечень!$F$6:$F$51,MATCH(H363,Перечень!$A$6:$A$51,0)),""))</f>
@@ -27658,7 +27668,7 @@
       </c>
       <c r="R363" s="41" t="str">
         <f aca="true">IF(C363="","",IF(M363="","Нет сведений",IF(M363&lt;TODAY(),"Просрочен",IF(M363-TODAY()&lt;=30,"Истекает","В срок"))))</f>
-        <v>Нет сведений</v>
+        <v>В срок</v>
       </c>
       <c r="S363" s="41" t="str">
         <f aca="false">IF(AND(N363="Да",O363=""),"Не пройдено","")</f>
@@ -27701,11 +27711,13 @@
         <f aca="false">IF(C364="","",IFERROR(INDEX(Перечень!$D$6:$D$51,MATCH(H364,Перечень!$A$6:$A$51,0)),12))</f>
         <v>12</v>
       </c>
-      <c r="K364" s="40"/>
+      <c r="K364" s="40" t="n">
+        <v>46296</v>
+      </c>
       <c r="L364" s="40"/>
-      <c r="M364" s="37" t="str">
+      <c r="M364" s="37" t="n">
         <f aca="false">IF(AND(K364="",L364=""),"",EDATE(MAX(K364,L364),J364))</f>
-        <v/>
+        <v>46661</v>
       </c>
       <c r="N364" s="41" t="str">
         <f aca="false">IF(C364="","",IFERROR(INDEX(Перечень!$F$6:$F$51,MATCH(H364,Перечень!$A$6:$A$51,0)),""))</f>
@@ -27722,7 +27734,7 @@
       </c>
       <c r="R364" s="41" t="str">
         <f aca="true">IF(C364="","",IF(M364="","Нет сведений",IF(M364&lt;TODAY(),"Просрочен",IF(M364-TODAY()&lt;=30,"Истекает","В срок"))))</f>
-        <v>Нет сведений</v>
+        <v>В срок</v>
       </c>
       <c r="S364" s="41" t="str">
         <f aca="false">IF(AND(N364="Да",O364=""),"Не пройдено","")</f>
